--- a/src/test/resources/Reader/Apollo247_TestData.xlsx
+++ b/src/test/resources/Reader/Apollo247_TestData.xlsx
@@ -1,13 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shyam Sundar\OneDrive\Desktop\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43F3F67F-6C32-4105-A278-178A7104CA5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="BMI" sheetId="1" r:id="rId1"/>
+    <sheet name="Patients_Data" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -18,12 +25,156 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="41">
+  <si>
+    <t>Height (ft)</t>
+  </si>
+  <si>
+    <t>Weight (kg)</t>
+  </si>
+  <si>
+    <t>Expected</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>Underweight</t>
+  </si>
+  <si>
+    <t>Overweight</t>
+  </si>
+  <si>
+    <t>Obese</t>
+  </si>
+  <si>
+    <t>FirstName</t>
+  </si>
+  <si>
+    <t>LastName</t>
+  </si>
+  <si>
+    <t>DateOfBirth</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>Relation</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Rahul</t>
+  </si>
+  <si>
+    <t>Kumar</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>Brother</t>
+  </si>
+  <si>
+    <t>rahul.kumar@gmail.com</t>
+  </si>
+  <si>
+    <t>Priya</t>
+  </si>
+  <si>
+    <t>Sharma</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>Sister</t>
+  </si>
+  <si>
+    <t>priya.sharma@gmail.com</t>
+  </si>
+  <si>
+    <t>Arjun</t>
+  </si>
+  <si>
+    <t>Reddy</t>
+  </si>
+  <si>
+    <t>Father</t>
+  </si>
+  <si>
+    <t>arjun.reddy@gmail.com</t>
+  </si>
+  <si>
+    <t>Lakshmi</t>
+  </si>
+  <si>
+    <t>Devi</t>
+  </si>
+  <si>
+    <t>Mother</t>
+  </si>
+  <si>
+    <t>lakshmi.devi@gmail.com</t>
+  </si>
+  <si>
+    <t>Kiran</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>Son</t>
+  </si>
+  <si>
+    <t>kiran.kumar@gmail.com</t>
+  </si>
+  <si>
+    <t>TestName</t>
+  </si>
+  <si>
+    <t>CBC Test</t>
+  </si>
+  <si>
+    <t>PPBS Test</t>
+  </si>
+  <si>
+    <t>FBS Test</t>
+  </si>
+  <si>
+    <t>Hemogram Test</t>
+  </si>
+  <si>
+    <t>vitamin D Test</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -37,7 +188,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,14 +196,52 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -330,10 +519,299 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.08984375" customWidth="1"/>
+    <col min="2" max="2" width="18.453125" customWidth="1"/>
+    <col min="3" max="3" width="17.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="2">
+        <v>5.7</v>
+      </c>
+      <c r="B2" s="2">
+        <v>65</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2">
+        <v>50</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="B4" s="2">
+        <v>70</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
+        <v>5.8</v>
+      </c>
+      <c r="B5" s="2">
+        <v>80</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
+        <v>5.2</v>
+      </c>
+      <c r="B6" s="2">
+        <v>45</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
+        <v>6.1</v>
+      </c>
+      <c r="B7" s="2">
+        <v>90</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
+        <v>5</v>
+      </c>
+      <c r="B8" s="2">
+        <v>40</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
+        <v>5.9</v>
+      </c>
+      <c r="B9" s="2">
+        <v>75</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
+        <v>5.7</v>
+      </c>
+      <c r="B10" s="2">
+        <v>101</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
+        <v>6</v>
+      </c>
+      <c r="B11" s="2">
+        <v>106</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2FECFBD-25D6-4F6C-91BB-5A6C18ADD79D}">
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="5">
+        <v>36022</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="5">
+        <v>36607</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="5">
+        <v>35008</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="5">
+        <v>27406</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="5">
+        <v>40359</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G6" r:id="rId1" display="mailto:kiran.kumar@gmail.com" xr:uid="{8E4FF1C4-A486-4E00-8CAC-5B0751AA02CA}"/>
+    <hyperlink ref="G5" r:id="rId2" display="mailto:lakshmi.devi@gmail.com" xr:uid="{56886F69-2DA0-4471-BC73-857F2BD266E1}"/>
+    <hyperlink ref="G4" r:id="rId3" display="mailto:arjun.reddy@gmail.com" xr:uid="{E81D8ACA-4202-454E-88EE-0DC02BFA7560}"/>
+    <hyperlink ref="G3" r:id="rId4" display="mailto:priya.sharma@gmail.com" xr:uid="{1D8F99EF-3E43-4DDA-98DA-3BF0942722F8}"/>
+    <hyperlink ref="G2" r:id="rId5" display="mailto:rahul.kumar@gmail.com" xr:uid="{3AFE8805-37A3-476D-8A50-2E016D8D5CA8}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/src/test/resources/Reader/Apollo247_TestData.xlsx
+++ b/src/test/resources/Reader/Apollo247_TestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shyam Sundar\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43F3F67F-6C32-4105-A278-178A7104CA5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87F873BA-3D4E-4150-8BD9-A29E317C2ACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="35">
   <si>
     <t>Height (ft)</t>
   </si>
@@ -131,24 +131,6 @@
   </si>
   <si>
     <t>kiran.kumar@gmail.com</t>
-  </si>
-  <si>
-    <t>TestName</t>
-  </si>
-  <si>
-    <t>CBC Test</t>
-  </si>
-  <si>
-    <t>PPBS Test</t>
-  </si>
-  <si>
-    <t>FBS Test</t>
-  </si>
-  <si>
-    <t>Hemogram Test</t>
-  </si>
-  <si>
-    <t>vitamin D Test</t>
   </si>
 </sst>
 </file>
@@ -656,161 +638,142 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2FECFBD-25D6-4F6C-91BB-5A6C18ADD79D}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="10.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="7.7265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="5">
+      <c r="C2" s="5">
         <v>36022</v>
       </c>
+      <c r="D2" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="E2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="5">
+        <v>36607</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="5">
+        <v>35008</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="5">
-        <v>36607</v>
-      </c>
-      <c r="E3" s="4" t="s">
+      <c r="E4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="5">
+        <v>27406</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="5">
-        <v>35008</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" s="5">
-        <v>27406</v>
-      </c>
       <c r="E5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="F5" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="5">
+      <c r="C6" s="5">
         <v>40359</v>
       </c>
+      <c r="D6" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="E6" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="F6" s="6" t="s">
         <v>34</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G6" r:id="rId1" display="mailto:kiran.kumar@gmail.com" xr:uid="{8E4FF1C4-A486-4E00-8CAC-5B0751AA02CA}"/>
-    <hyperlink ref="G5" r:id="rId2" display="mailto:lakshmi.devi@gmail.com" xr:uid="{56886F69-2DA0-4471-BC73-857F2BD266E1}"/>
-    <hyperlink ref="G4" r:id="rId3" display="mailto:arjun.reddy@gmail.com" xr:uid="{E81D8ACA-4202-454E-88EE-0DC02BFA7560}"/>
-    <hyperlink ref="G3" r:id="rId4" display="mailto:priya.sharma@gmail.com" xr:uid="{1D8F99EF-3E43-4DDA-98DA-3BF0942722F8}"/>
-    <hyperlink ref="G2" r:id="rId5" display="mailto:rahul.kumar@gmail.com" xr:uid="{3AFE8805-37A3-476D-8A50-2E016D8D5CA8}"/>
+    <hyperlink ref="F6" r:id="rId1" display="mailto:kiran.kumar@gmail.com" xr:uid="{8E4FF1C4-A486-4E00-8CAC-5B0751AA02CA}"/>
+    <hyperlink ref="F5" r:id="rId2" display="mailto:lakshmi.devi@gmail.com" xr:uid="{56886F69-2DA0-4471-BC73-857F2BD266E1}"/>
+    <hyperlink ref="F4" r:id="rId3" display="mailto:arjun.reddy@gmail.com" xr:uid="{E81D8ACA-4202-454E-88EE-0DC02BFA7560}"/>
+    <hyperlink ref="F3" r:id="rId4" display="mailto:priya.sharma@gmail.com" xr:uid="{1D8F99EF-3E43-4DDA-98DA-3BF0942722F8}"/>
+    <hyperlink ref="F2" r:id="rId5" display="mailto:rahul.kumar@gmail.com" xr:uid="{3AFE8805-37A3-476D-8A50-2E016D8D5CA8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/test/resources/Reader/Apollo247_TestData.xlsx
+++ b/src/test/resources/Reader/Apollo247_TestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shyam Sundar\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87F873BA-3D4E-4150-8BD9-A29E317C2ACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE1200AA-3320-4C2B-BF0F-F0EE70AC6368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="40">
   <si>
     <t>Height (ft)</t>
   </si>
@@ -131,13 +131,28 @@
   </si>
   <si>
     <t>kiran.kumar@gmail.com</t>
+  </si>
+  <si>
+    <t>12/03/2002</t>
+  </si>
+  <si>
+    <t>12/03/2006</t>
+  </si>
+  <si>
+    <t>15/02/2000</t>
+  </si>
+  <si>
+    <t>12/11/1998</t>
+  </si>
+  <si>
+    <t>01/07/2008</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -157,6 +172,12 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -212,14 +233,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -647,7 +668,7 @@
     <col min="6" max="6" width="22.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
@@ -674,8 +695,8 @@
       <c r="B2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="5">
-        <v>36022</v>
+      <c r="C2" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>15</v>
@@ -683,7 +704,7 @@
       <c r="E2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -694,8 +715,8 @@
       <c r="B3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="5">
-        <v>36607</v>
+      <c r="C3" s="7" t="s">
+        <v>37</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>20</v>
@@ -703,7 +724,7 @@
       <c r="E3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>22</v>
       </c>
     </row>
@@ -714,8 +735,8 @@
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="5">
-        <v>35008</v>
+      <c r="C4" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>15</v>
@@ -723,7 +744,7 @@
       <c r="E4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="5" t="s">
         <v>26</v>
       </c>
     </row>
@@ -734,8 +755,8 @@
       <c r="B5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="5">
-        <v>27406</v>
+      <c r="C5" s="7" t="s">
+        <v>39</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>20</v>
@@ -743,7 +764,7 @@
       <c r="E5" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="5" t="s">
         <v>30</v>
       </c>
     </row>
@@ -754,8 +775,8 @@
       <c r="B6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="5">
-        <v>40359</v>
+      <c r="C6" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>32</v>
@@ -763,11 +784,12 @@
       <c r="E6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="5" t="s">
         <v>34</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="F6" r:id="rId1" display="mailto:kiran.kumar@gmail.com" xr:uid="{8E4FF1C4-A486-4E00-8CAC-5B0751AA02CA}"/>
     <hyperlink ref="F5" r:id="rId2" display="mailto:lakshmi.devi@gmail.com" xr:uid="{56886F69-2DA0-4471-BC73-857F2BD266E1}"/>

--- a/src/test/resources/Reader/Apollo247_TestData.xlsx
+++ b/src/test/resources/Reader/Apollo247_TestData.xlsx
@@ -4,13 +4,15 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="2448" windowWidth="8436" windowHeight="2448" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="BMI" sheetId="1" r:id="rId1"/>
-    <sheet name="FamilyMembers" sheetId="2" r:id="rId2"/>
+    <sheet name="Patients_Data" sheetId="2" r:id="rId2"/>
+    <sheet name="FamilyMembers" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="0"/>
+  <oleSize ref="A1:H7"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -20,12 +22,126 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>Height</t>
-  </si>
-  <si>
-    <t>Weight</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="49">
+  <si>
+    <t>Height (ft)</t>
+  </si>
+  <si>
+    <t>Weight (kg)</t>
+  </si>
+  <si>
+    <t>Expected</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>Underweight</t>
+  </si>
+  <si>
+    <t>Overweight</t>
+  </si>
+  <si>
+    <t>Obese</t>
+  </si>
+  <si>
+    <t>FirstName</t>
+  </si>
+  <si>
+    <t>LastName</t>
+  </si>
+  <si>
+    <t>DateOfBirth</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>Relation</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Rahul</t>
+  </si>
+  <si>
+    <t>Kumar</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>Brother</t>
+  </si>
+  <si>
+    <t>rahul.kumar@gmail.com</t>
+  </si>
+  <si>
+    <t>Priya</t>
+  </si>
+  <si>
+    <t>Sharma</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>Sister</t>
+  </si>
+  <si>
+    <t>priya.sharma@gmail.com</t>
+  </si>
+  <si>
+    <t>Arjun</t>
+  </si>
+  <si>
+    <t>Reddy</t>
+  </si>
+  <si>
+    <t>Father</t>
+  </si>
+  <si>
+    <t>arjun.reddy@gmail.com</t>
+  </si>
+  <si>
+    <t>Lakshmi</t>
+  </si>
+  <si>
+    <t>Devi</t>
+  </si>
+  <si>
+    <t>Mother</t>
+  </si>
+  <si>
+    <t>lakshmi.devi@gmail.com</t>
+  </si>
+  <si>
+    <t>Kiran</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>Son</t>
+  </si>
+  <si>
+    <t>kiran.kumar@gmail.com</t>
+  </si>
+  <si>
+    <t>12/03/2002</t>
+  </si>
+  <si>
+    <t>12/03/2006</t>
+  </si>
+  <si>
+    <t>15/02/2000</t>
+  </si>
+  <si>
+    <t>12/11/1998</t>
+  </si>
+  <si>
+    <t>01/07/2008</t>
   </si>
   <si>
     <t>firstName</t>
@@ -37,29 +153,54 @@
     <t>dob</t>
   </si>
   <si>
+    <t>Vishva</t>
+  </si>
+  <si>
     <t>D</t>
   </si>
   <si>
+    <t>Prithvi</t>
+  </si>
+  <si>
     <t>N</t>
   </si>
   <si>
-    <t>Prithvi</t>
-  </si>
-  <si>
-    <t>Vishva</t>
-  </si>
-  <si>
-    <t>30-02-2000</t>
+    <t>31/05/1998</t>
+  </si>
+  <si>
+    <t>12/03/2004</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -73,7 +214,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -81,15 +222,55 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -368,42 +549,133 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="1" max="1" width="18.109375" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" customWidth="1"/>
+    <col min="3" max="3" width="17.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>170</v>
-      </c>
-      <c r="B2">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="2">
+        <v>5.7</v>
+      </c>
+      <c r="B2" s="2">
+        <v>65</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2">
+        <v>50</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="B4" s="2">
+        <v>70</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
+        <v>5.8</v>
+      </c>
+      <c r="B5" s="2">
         <v>80</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>160</v>
-      </c>
-      <c r="B3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>155</v>
-      </c>
-      <c r="B4">
+      <c r="C5" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
+        <v>5.2</v>
+      </c>
+      <c r="B6" s="2">
         <v>45</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
+        <v>6.1</v>
+      </c>
+      <c r="B7" s="2">
+        <v>90</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
+        <v>5</v>
+      </c>
+      <c r="B8" s="2">
+        <v>40</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
+        <v>5.9</v>
+      </c>
+      <c r="B9" s="2">
+        <v>75</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
+        <v>5.7</v>
+      </c>
+      <c r="B10" s="2">
+        <v>101</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
+        <v>6</v>
+      </c>
+      <c r="B11" s="2">
+        <v>106</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -413,43 +685,187 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="F6" r:id="rId1" display="mailto:kiran.kumar@gmail.com"/>
+    <hyperlink ref="F5" r:id="rId2" display="mailto:lakshmi.devi@gmail.com"/>
+    <hyperlink ref="F4" r:id="rId3" display="mailto:arjun.reddy@gmail.com"/>
+    <hyperlink ref="F3" r:id="rId4" display="mailto:priya.sharma@gmail.com"/>
+    <hyperlink ref="F2" r:id="rId5" display="mailto:rahul.kumar@gmail.com"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="11.44140625" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="1">
-        <v>37508</v>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/Reader/Apollo247_TestData.xlsx
+++ b/src/test/resources/Reader/Apollo247_TestData.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shyam Sundar\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE1200AA-3320-4C2B-BF0F-F0EE70AC6368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A18B651-A12A-4DE8-8625-DD72358DC96C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BMI" sheetId="1" r:id="rId1"/>
     <sheet name="Patients_Data" sheetId="2" r:id="rId2"/>
+    <sheet name="FamilyMembers" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="49">
   <si>
     <t>Height (ft)</t>
   </si>
@@ -146,6 +147,33 @@
   </si>
   <si>
     <t>01/07/2008</t>
+  </si>
+  <si>
+    <t>firstName</t>
+  </si>
+  <si>
+    <t>lastName</t>
+  </si>
+  <si>
+    <t>dob</t>
+  </si>
+  <si>
+    <t>Vishva</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>Prithvi</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>31/05/1998</t>
+  </si>
+  <si>
+    <t>12/03/2004</t>
   </si>
 </sst>
 </file>
@@ -219,7 +247,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -242,6 +270,9 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -799,4 +830,50 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BE65286-7997-4135-A8D2-DDAC29E69C7A}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="10.08984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/test/resources/Reader/Apollo247_TestData.xlsx
+++ b/src/test/resources/Reader/Apollo247_TestData.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shyam Sundar\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7813A325-64A3-4197-88EB-6113563BB9A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1742AD06-6983-47BA-93C3-C31A762C4029}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BMI" sheetId="1" r:id="rId1"/>
-    <sheet name="Patients_Data" sheetId="2" r:id="rId2"/>
-    <sheet name="FamilyMembers" sheetId="3" r:id="rId3"/>
-    <sheet name="Policy_purchase_Data" sheetId="4" r:id="rId4"/>
+    <sheet name="BuyMedicine" sheetId="5" r:id="rId2"/>
+    <sheet name="Patients_Data" sheetId="2" r:id="rId3"/>
+    <sheet name="FamilyMembers" sheetId="3" r:id="rId4"/>
+    <sheet name="Policy_purchase_Data" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="284">
   <si>
     <t>Height (ft)</t>
   </si>
@@ -859,6 +860,27 @@
   </si>
   <si>
     <t>ProposerFN</t>
+  </si>
+  <si>
+    <t>MEDICINE NAME</t>
+  </si>
+  <si>
+    <t>Calpol 650</t>
+  </si>
+  <si>
+    <t>Digene Tablet</t>
+  </si>
+  <si>
+    <t>Gelusil Syrup</t>
+  </si>
+  <si>
+    <t>Benadryl Syrup</t>
+  </si>
+  <si>
+    <t>Vicks VapoRub</t>
+  </si>
+  <si>
+    <t>Moov Spray</t>
   </si>
 </sst>
 </file>
@@ -1182,19 +1204,28 @@
     <xf numFmtId="49" fontId="7" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1205,15 +1236,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1638,6 +1660,54 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B46A366B-4A49-4F81-9245-154B6D9B7EE7}">
+  <dimension ref="A1:A7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" s="9" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" s="9" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" s="9" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" s="9" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" s="9" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" s="9" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" s="9" t="s">
+        <v>283</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2FECFBD-25D6-4F6C-91BB-5A6C18ADD79D}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:F6"/>
@@ -1782,7 +1852,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BE65286-7997-4135-A8D2-DDAC29E69C7A}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:C3"/>
@@ -1829,7 +1899,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F6F6BB4-2A7A-4EE8-A91D-627425662417}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A2:AU12"/>
@@ -1879,7 +1949,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="40" t="s">
         <v>49</v>
       </c>
       <c r="B2" s="41"/>
@@ -1930,7 +2000,7 @@
       <c r="AU2" s="41"/>
     </row>
     <row r="3" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="42" t="s">
         <v>50</v>
       </c>
       <c r="B3" s="41"/>
@@ -1940,7 +2010,7 @@
       </c>
       <c r="E3" s="41"/>
       <c r="F3" s="41"/>
-      <c r="G3" s="46" t="s">
+      <c r="G3" s="49" t="s">
         <v>52</v>
       </c>
       <c r="H3" s="41"/>
@@ -1948,36 +2018,36 @@
       <c r="J3" s="41"/>
       <c r="K3" s="41"/>
       <c r="L3" s="41"/>
-      <c r="M3" s="47" t="s">
+      <c r="M3" s="50" t="s">
         <v>53</v>
       </c>
       <c r="N3" s="41"/>
       <c r="O3" s="41"/>
       <c r="P3" s="41"/>
       <c r="Q3" s="41"/>
-      <c r="R3" s="43" t="s">
+      <c r="R3" s="47" t="s">
         <v>54</v>
       </c>
       <c r="S3" s="41"/>
       <c r="T3" s="41"/>
       <c r="U3" s="41"/>
       <c r="V3" s="41"/>
-      <c r="W3" s="51" t="s">
+      <c r="W3" s="43" t="s">
         <v>55</v>
       </c>
       <c r="X3" s="41"/>
       <c r="Y3" s="41"/>
-      <c r="Z3" s="45" t="s">
+      <c r="Z3" s="48" t="s">
         <v>56</v>
       </c>
       <c r="AA3" s="41"/>
       <c r="AB3" s="41"/>
-      <c r="AC3" s="48" t="s">
+      <c r="AC3" s="51" t="s">
         <v>57</v>
       </c>
       <c r="AD3" s="41"/>
       <c r="AE3" s="41"/>
-      <c r="AF3" s="42" t="s">
+      <c r="AF3" s="46" t="s">
         <v>58</v>
       </c>
       <c r="AG3" s="41"/>
@@ -1987,7 +2057,7 @@
       <c r="AK3" s="41"/>
       <c r="AL3" s="41"/>
       <c r="AM3" s="41"/>
-      <c r="AN3" s="50" t="s">
+      <c r="AN3" s="42" t="s">
         <v>59</v>
       </c>
       <c r="AO3" s="41"/>
@@ -2835,7 +2905,7 @@
       </c>
     </row>
     <row r="11" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A11" s="40" t="s">
+      <c r="A11" s="45" t="s">
         <v>218</v>
       </c>
       <c r="B11" s="41"/>
@@ -3030,11 +3100,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A2:AU2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="W3:Y3"/>
-    <mergeCell ref="AN3:AP3"/>
-    <mergeCell ref="AQ3:AU3"/>
     <mergeCell ref="A11:AU11"/>
     <mergeCell ref="AF3:AM3"/>
     <mergeCell ref="R3:V3"/>
@@ -3043,6 +3108,11 @@
     <mergeCell ref="G3:L3"/>
     <mergeCell ref="M3:Q3"/>
     <mergeCell ref="AC3:AE3"/>
+    <mergeCell ref="A2:AU2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="W3:Y3"/>
+    <mergeCell ref="AN3:AP3"/>
+    <mergeCell ref="AQ3:AU3"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/test/resources/Reader/Apollo247_TestData.xlsx
+++ b/src/test/resources/Reader/Apollo247_TestData.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\roshi\AppData\Local\Packages\5319275A.WhatsAppDesktop_cv1g1gvanyjgm\LocalState\sessions\486D6DECC99E35A76364A19DBA20A1300C25A016\transfers\2026-17\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Swetha\OneDrive\Documents\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{756C214D-D6E5-411D-B533-DF8982900D7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1694E94E-1E7A-460D-903A-E31B633E3199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="22656" windowHeight="12072" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BMI" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="BuyMedicine" sheetId="5" r:id="rId2"/>
+    <sheet name="Patients_Data" sheetId="2" r:id="rId3"/>
+    <sheet name="FamilyMembers" sheetId="3" r:id="rId4"/>
+    <sheet name="Policy_purchase_Data" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,31 +29,865 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
-  <si>
-    <t>Height</t>
-  </si>
-  <si>
-    <t>Weight</t>
-  </si>
-  <si>
-    <t>MedicineName</t>
-  </si>
-  <si>
-    <t>Dolo-650 Tablet</t>
-  </si>
-  <si>
-    <t>Crocin Advance</t>
-  </si>
-  <si>
-    <t>Volini Gel</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="284">
+  <si>
+    <t>Height (ft)</t>
+  </si>
+  <si>
+    <t>Weight (kg)</t>
+  </si>
+  <si>
+    <t>Expected</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>Underweight</t>
+  </si>
+  <si>
+    <t>Overweight</t>
+  </si>
+  <si>
+    <t>Obese</t>
+  </si>
+  <si>
+    <t>FirstName</t>
+  </si>
+  <si>
+    <t>LastName</t>
+  </si>
+  <si>
+    <t>DateOfBirth</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>Relation</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Rahul</t>
+  </si>
+  <si>
+    <t>Kumar</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>Brother</t>
+  </si>
+  <si>
+    <t>rahul.kumar@gmail.com</t>
+  </si>
+  <si>
+    <t>Priya</t>
+  </si>
+  <si>
+    <t>Sharma</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>Sister</t>
+  </si>
+  <si>
+    <t>priya.sharma@gmail.com</t>
+  </si>
+  <si>
+    <t>Arjun</t>
+  </si>
+  <si>
+    <t>Reddy</t>
+  </si>
+  <si>
+    <t>Father</t>
+  </si>
+  <si>
+    <t>arjun.reddy@gmail.com</t>
+  </si>
+  <si>
+    <t>Lakshmi</t>
+  </si>
+  <si>
+    <t>Devi</t>
+  </si>
+  <si>
+    <t>Mother</t>
+  </si>
+  <si>
+    <t>lakshmi.devi@gmail.com</t>
+  </si>
+  <si>
+    <t>Kiran</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>Son</t>
+  </si>
+  <si>
+    <t>kiran.kumar@gmail.com</t>
+  </si>
+  <si>
+    <t>12/03/2002</t>
+  </si>
+  <si>
+    <t>12/03/2006</t>
+  </si>
+  <si>
+    <t>15/02/2000</t>
+  </si>
+  <si>
+    <t>12/11/1998</t>
+  </si>
+  <si>
+    <t>01/07/2008</t>
+  </si>
+  <si>
+    <t>firstName</t>
+  </si>
+  <si>
+    <t>lastName</t>
+  </si>
+  <si>
+    <t>dob</t>
+  </si>
+  <si>
+    <t>Vishva</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>Prithvi</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>31/05/1998</t>
+  </si>
+  <si>
+    <t>12/03/2004</t>
+  </si>
+  <si>
+    <t>Apollo247 – BDD Cucumber Excel Data Provider  |  Sheet: Policy_purchase_Data  |  File: Apollo247_TestData.xlsx</t>
+  </si>
+  <si>
+    <t>TC Info</t>
+  </si>
+  <si>
+    <t>Member Selection</t>
+  </si>
+  <si>
+    <t>Step1 – Member Details</t>
+  </si>
+  <si>
+    <t>Step2 – Medical Questions</t>
+  </si>
+  <si>
+    <t>Step3 – Proposer Details</t>
+  </si>
+  <si>
+    <t>Step4 – KYC</t>
+  </si>
+  <si>
+    <t>Step5 – Address Proof</t>
+  </si>
+  <si>
+    <t>Step6 – Address</t>
+  </si>
+  <si>
+    <t>Step7 – Nominee &amp; Appointee</t>
+  </si>
+  <si>
+    <t>Step8 – Bank</t>
+  </si>
+  <si>
+    <t>Policy / Payment Validation</t>
+  </si>
+  <si>
+    <t>TestCaseID</t>
+  </si>
+  <si>
+    <t>Scenario</t>
+  </si>
+  <si>
+    <t>RunFlag</t>
+  </si>
+  <si>
+    <t>MemberType</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Height_ft</t>
+  </si>
+  <si>
+    <t>Height_in</t>
+  </si>
+  <si>
+    <t>Weight_kg</t>
+  </si>
+  <si>
+    <t>MedQ1</t>
+  </si>
+  <si>
+    <t>MedQ2</t>
+  </si>
+  <si>
+    <t>MedQ3</t>
+  </si>
+  <si>
+    <t>MedQ4</t>
+  </si>
+  <si>
+    <t>MedQ5</t>
+  </si>
+  <si>
+    <t>Mobile</t>
+  </si>
+  <si>
+    <t>AltMobile</t>
+  </si>
+  <si>
+    <t>PAN</t>
+  </si>
+  <si>
+    <t>KYC_DocType</t>
+  </si>
+  <si>
+    <t>KYC_DocNumber</t>
+  </si>
+  <si>
+    <t>KYC_Upload</t>
+  </si>
+  <si>
+    <t>AddrProof_DocType</t>
+  </si>
+  <si>
+    <t>AddrProof_DocNumber</t>
+  </si>
+  <si>
+    <t>AddrProof_Upload</t>
+  </si>
+  <si>
+    <t>StreetAddress</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>Pincode</t>
+  </si>
+  <si>
+    <t>Nom_FirstName</t>
+  </si>
+  <si>
+    <t>Nom_LastName</t>
+  </si>
+  <si>
+    <t>Nom_Relation</t>
+  </si>
+  <si>
+    <t>Nom_DOB</t>
+  </si>
+  <si>
+    <t>App_FirstName</t>
+  </si>
+  <si>
+    <t>App_LastName</t>
+  </si>
+  <si>
+    <t>App_DOB</t>
+  </si>
+  <si>
+    <t>App_Relation</t>
+  </si>
+  <si>
+    <t>BankAccNumber</t>
+  </si>
+  <si>
+    <t>BankAccType</t>
+  </si>
+  <si>
+    <t>IFSC_Code</t>
+  </si>
+  <si>
+    <t>PolicyHolderName</t>
+  </si>
+  <si>
+    <t>BuyNow</t>
+  </si>
+  <si>
+    <t>PayVerify</t>
+  </si>
+  <si>
+    <t>PaymentOptions</t>
+  </si>
+  <si>
+    <t>ToPay</t>
+  </si>
+  <si>
+    <t>TC_INS_001</t>
+  </si>
+  <si>
+    <t>Purchase Insurance – Happy Path</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Self</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>sg</t>
+  </si>
+  <si>
+    <t>anand</t>
+  </si>
+  <si>
+    <t>April 15, 2004</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>sganand@gmail.com</t>
+  </si>
+  <si>
+    <t>7402025339</t>
+  </si>
+  <si>
+    <t>SM</t>
+  </si>
+  <si>
+    <t>AFZPK7190K</t>
+  </si>
+  <si>
+    <t>Aadhar Card</t>
+  </si>
+  <si>
+    <t>273794621727</t>
+  </si>
+  <si>
+    <t>kyc_doc.jpg</t>
+  </si>
+  <si>
+    <t>addr_doc.jpg</t>
+  </si>
+  <si>
+    <t>No 8 xyz</t>
+  </si>
+  <si>
+    <t>gpd</t>
+  </si>
+  <si>
+    <t>601201</t>
+  </si>
+  <si>
+    <t>Neil</t>
+  </si>
+  <si>
+    <t>Jun</t>
+  </si>
+  <si>
+    <t>Wife</t>
+  </si>
+  <si>
+    <t>April 15, 2026</t>
+  </si>
+  <si>
+    <t>Jack</t>
+  </si>
+  <si>
+    <t>Haltman</t>
+  </si>
+  <si>
+    <t>April 10, 2008</t>
+  </si>
+  <si>
+    <t>50200027074321</t>
+  </si>
+  <si>
+    <t>Savings</t>
+  </si>
+  <si>
+    <t>HDFC0000001</t>
+  </si>
+  <si>
+    <t>sg anand</t>
+  </si>
+  <si>
+    <t>Buy Now</t>
+  </si>
+  <si>
+    <t>payment</t>
+  </si>
+  <si>
+    <t>Payment Options</t>
+  </si>
+  <si>
+    <t>To Pay</t>
+  </si>
+  <si>
+    <t>TC_INS_002</t>
+  </si>
+  <si>
+    <t>Purchase Insurance – Female Spouse</t>
+  </si>
+  <si>
+    <t>Spouse</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>February 20, 1996</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>9876543210</t>
+  </si>
+  <si>
+    <t>Mrs</t>
+  </si>
+  <si>
+    <t>BCDPK1234L</t>
+  </si>
+  <si>
+    <t>Passport</t>
+  </si>
+  <si>
+    <t>K1234567</t>
+  </si>
+  <si>
+    <t>passport.jpg</t>
+  </si>
+  <si>
+    <t>addr_passport.jpg</t>
+  </si>
+  <si>
+    <t>No 12 abc</t>
+  </si>
+  <si>
+    <t>Chennai</t>
+  </si>
+  <si>
+    <t>600001</t>
+  </si>
+  <si>
+    <t>Husband</t>
+  </si>
+  <si>
+    <t>June 10, 1993</t>
+  </si>
+  <si>
+    <t>Ravi</t>
+  </si>
+  <si>
+    <t>March 05, 2010</t>
+  </si>
+  <si>
+    <t>40100012345678</t>
+  </si>
+  <si>
+    <t>ICIC0001234</t>
+  </si>
+  <si>
+    <t>Priya Sharma</t>
+  </si>
+  <si>
+    <t>TC_INS_003</t>
+  </si>
+  <si>
+    <t>Purchase Insurance – Father as Member</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>Ramesh</t>
+  </si>
+  <si>
+    <t>Anand</t>
+  </si>
+  <si>
+    <t>January 01, 1972</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>ramesh.anand@gmail.com</t>
+  </si>
+  <si>
+    <t>9123456780</t>
+  </si>
+  <si>
+    <t>Mr</t>
+  </si>
+  <si>
+    <t>CDFPK5678M</t>
+  </si>
+  <si>
+    <t>Voter ID</t>
+  </si>
+  <si>
+    <t>TN/01/123/456789</t>
+  </si>
+  <si>
+    <t>voterid.jpg</t>
+  </si>
+  <si>
+    <t>addr_voterid.jpg</t>
+  </si>
+  <si>
+    <t>No 25 def</t>
+  </si>
+  <si>
+    <t>Coimbatore</t>
+  </si>
+  <si>
+    <t>641001</t>
+  </si>
+  <si>
+    <t>30200098765432</t>
+  </si>
+  <si>
+    <t>Current</t>
+  </si>
+  <si>
+    <t>SBIN0001001</t>
+  </si>
+  <si>
+    <t>Ramesh Anand</t>
+  </si>
+  <si>
+    <t>TC_INS_004</t>
+  </si>
+  <si>
+    <t>Purchase Insurance – Child Member</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>December 11, 2014</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>8765432109</t>
+  </si>
+  <si>
+    <t>DFGPK9012N</t>
+  </si>
+  <si>
+    <t>123456789012</t>
+  </si>
+  <si>
+    <t>kyc_aadhar2.jpg</t>
+  </si>
+  <si>
+    <t>addr_aadhar2.jpg</t>
+  </si>
+  <si>
+    <t>No 5 ghi</t>
+  </si>
+  <si>
+    <t>Madurai</t>
+  </si>
+  <si>
+    <t>625001</t>
+  </si>
+  <si>
+    <t>July 01, 1976</t>
+  </si>
+  <si>
+    <t>20300076543210</t>
+  </si>
+  <si>
+    <t>HDFC0001002</t>
+  </si>
+  <si>
+    <t>Arjun Reddy</t>
+  </si>
+  <si>
+    <t>TC_INS_005</t>
+  </si>
+  <si>
+    <t>Purchase Insurance – Mother as Member</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>7654321098</t>
+  </si>
+  <si>
+    <t>EFHPK3456O</t>
+  </si>
+  <si>
+    <t>Driving License</t>
+  </si>
+  <si>
+    <t>TN-0120110012345</t>
+  </si>
+  <si>
+    <t>dl.jpg</t>
+  </si>
+  <si>
+    <t>addr_dl.jpg</t>
+  </si>
+  <si>
+    <t>No 3 jkl</t>
+  </si>
+  <si>
+    <t>Trichy</t>
+  </si>
+  <si>
+    <t>620001</t>
+  </si>
+  <si>
+    <t>December 03, 2006</t>
+  </si>
+  <si>
+    <t>10400054321098</t>
+  </si>
+  <si>
+    <t>AXIS0001003</t>
+  </si>
+  <si>
+    <t>Lakshmi Devi</t>
+  </si>
+  <si>
+    <t>⬆  getExcelData("Policy_purchase_Data", rowNum, colNum)  |  Headers = rowNum 2  |  Data starts at rowNum 3  (0-indexed rows)</t>
+  </si>
+  <si>
+    <t>col[0]</t>
+  </si>
+  <si>
+    <t>col[1]</t>
+  </si>
+  <si>
+    <t>col[2]</t>
+  </si>
+  <si>
+    <t>col[3]</t>
+  </si>
+  <si>
+    <t>col[4]</t>
+  </si>
+  <si>
+    <t>col[5]</t>
+  </si>
+  <si>
+    <t>col[6]</t>
+  </si>
+  <si>
+    <t>col[7]</t>
+  </si>
+  <si>
+    <t>col[8]</t>
+  </si>
+  <si>
+    <t>col[9]</t>
+  </si>
+  <si>
+    <t>col[10]</t>
+  </si>
+  <si>
+    <t>col[11]</t>
+  </si>
+  <si>
+    <t>col[12]</t>
+  </si>
+  <si>
+    <t>col[13]</t>
+  </si>
+  <si>
+    <t>col[14]</t>
+  </si>
+  <si>
+    <t>col[15]</t>
+  </si>
+  <si>
+    <t>col[16]</t>
+  </si>
+  <si>
+    <t>col[17]</t>
+  </si>
+  <si>
+    <t>col[18]</t>
+  </si>
+  <si>
+    <t>col[19]</t>
+  </si>
+  <si>
+    <t>col[20]</t>
+  </si>
+  <si>
+    <t>col[21]</t>
+  </si>
+  <si>
+    <t>col[22]</t>
+  </si>
+  <si>
+    <t>col[23]</t>
+  </si>
+  <si>
+    <t>col[24]</t>
+  </si>
+  <si>
+    <t>col[25]</t>
+  </si>
+  <si>
+    <t>col[26]</t>
+  </si>
+  <si>
+    <t>col[27]</t>
+  </si>
+  <si>
+    <t>col[28]</t>
+  </si>
+  <si>
+    <t>col[29]</t>
+  </si>
+  <si>
+    <t>col[30]</t>
+  </si>
+  <si>
+    <t>col[31]</t>
+  </si>
+  <si>
+    <t>col[32]</t>
+  </si>
+  <si>
+    <t>col[33]</t>
+  </si>
+  <si>
+    <t>col[34]</t>
+  </si>
+  <si>
+    <t>col[35]</t>
+  </si>
+  <si>
+    <t>col[36]</t>
+  </si>
+  <si>
+    <t>col[37]</t>
+  </si>
+  <si>
+    <t>col[38]</t>
+  </si>
+  <si>
+    <t>col[39]</t>
+  </si>
+  <si>
+    <t>col[40]</t>
+  </si>
+  <si>
+    <t>col[41]</t>
+  </si>
+  <si>
+    <t>col[42]</t>
+  </si>
+  <si>
+    <t>col[43]</t>
+  </si>
+  <si>
+    <t>col[44]</t>
+  </si>
+  <si>
+    <t>col[45]</t>
+  </si>
+  <si>
+    <t>col[46]</t>
+  </si>
+  <si>
+    <t>5 ft</t>
+  </si>
+  <si>
+    <t>6 ft</t>
+  </si>
+  <si>
+    <t>7 ft</t>
+  </si>
+  <si>
+    <t>8 ft</t>
+  </si>
+  <si>
+    <t>9 ft</t>
+  </si>
+  <si>
+    <t>5 in</t>
+  </si>
+  <si>
+    <t>6 in</t>
+  </si>
+  <si>
+    <t>7 in</t>
+  </si>
+  <si>
+    <t>8 in</t>
+  </si>
+  <si>
+    <t>9 in</t>
+  </si>
+  <si>
+    <t>ProposerFN</t>
+  </si>
+  <si>
+    <t>MEDICINE NAME</t>
+  </si>
+  <si>
+    <t>Calpol 650</t>
+  </si>
+  <si>
+    <t>Digene Tablet</t>
+  </si>
+  <si>
+    <t>Gelusil Syrup</t>
+  </si>
+  <si>
+    <t>Benadryl Syrup</t>
+  </si>
+  <si>
+    <t>Vicks VapoRub</t>
+  </si>
+  <si>
+    <t>Moov Spray</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -66,16 +903,156 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E75B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF375623"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF843C0C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF538135"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC55A11"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF833C00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEEAF1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF404040"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF99FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -83,11 +1060,42 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -95,12 +1103,153 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="9" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF99FF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -375,42 +1524,134 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B4"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="1" max="1" width="18.109375" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" customWidth="1"/>
+    <col min="3" max="3" width="17.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>170</v>
-      </c>
-      <c r="B2">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>5.7</v>
+      </c>
+      <c r="B2" s="2">
+        <v>65</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2">
+        <v>50</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="B4" s="2">
+        <v>70</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>5.8</v>
+      </c>
+      <c r="B5" s="2">
         <v>80</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>160</v>
-      </c>
-      <c r="B3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>155</v>
-      </c>
-      <c r="B4">
+      <c r="C5" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>5.2</v>
+      </c>
+      <c r="B6" s="2">
         <v>45</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>6.1</v>
+      </c>
+      <c r="B7" s="2">
+        <v>90</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>5</v>
+      </c>
+      <c r="B8" s="2">
+        <v>40</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>5.9</v>
+      </c>
+      <c r="B9" s="2">
+        <v>75</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>5.7</v>
+      </c>
+      <c r="B10" s="2">
+        <v>101</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>6</v>
+      </c>
+      <c r="B11" s="2">
+        <v>106</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -419,34 +1660,1461 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{582C0180-417E-47F0-BBBD-1DC2B287093A}">
-  <dimension ref="A1:A4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B46A366B-4A49-4F81-9245-154B6D9B7EE7}">
+  <dimension ref="A1:A7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.44140625" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>4</v>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>5</v>
+      <c r="A4" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>283</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2FECFBD-25D6-4F6C-91BB-5A6C18ADD79D}">
+  <sheetPr codeName="Sheet2"/>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="F6" r:id="rId1" display="mailto:kiran.kumar@gmail.com" xr:uid="{8E4FF1C4-A486-4E00-8CAC-5B0751AA02CA}"/>
+    <hyperlink ref="F5" r:id="rId2" display="mailto:lakshmi.devi@gmail.com" xr:uid="{56886F69-2DA0-4471-BC73-857F2BD266E1}"/>
+    <hyperlink ref="F4" r:id="rId3" display="mailto:arjun.reddy@gmail.com" xr:uid="{E81D8ACA-4202-454E-88EE-0DC02BFA7560}"/>
+    <hyperlink ref="F3" r:id="rId4" display="mailto:priya.sharma@gmail.com" xr:uid="{1D8F99EF-3E43-4DDA-98DA-3BF0942722F8}"/>
+    <hyperlink ref="F2" r:id="rId5" display="mailto:rahul.kumar@gmail.com" xr:uid="{3AFE8805-37A3-476D-8A50-2E016D8D5CA8}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BE65286-7997-4135-A8D2-DDAC29E69C7A}">
+  <sheetPr codeName="Sheet3"/>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F6F6BB4-2A7A-4EE8-A91D-627425662417}">
+  <sheetPr codeName="Sheet4"/>
+  <dimension ref="A2:AU12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.77734375" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875" style="25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.33203125" style="25" bestFit="1" customWidth="1"/>
+    <col min="13" max="17" width="7" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.77734375" customWidth="1"/>
+    <col min="19" max="20" width="10" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.77734375" customWidth="1"/>
+    <col min="23" max="23" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.77734375" customWidth="1"/>
+    <col min="26" max="26" width="10" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="8" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="10" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="10.77734375" customWidth="1"/>
+    <col min="37" max="37" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="10" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="10.77734375" customWidth="1"/>
+    <col min="43" max="43" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="10" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="6.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="A2" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="41"/>
+      <c r="O2" s="41"/>
+      <c r="P2" s="41"/>
+      <c r="Q2" s="41"/>
+      <c r="R2" s="41"/>
+      <c r="S2" s="41"/>
+      <c r="T2" s="41"/>
+      <c r="U2" s="41"/>
+      <c r="V2" s="41"/>
+      <c r="W2" s="41"/>
+      <c r="X2" s="41"/>
+      <c r="Y2" s="41"/>
+      <c r="Z2" s="41"/>
+      <c r="AA2" s="41"/>
+      <c r="AB2" s="41"/>
+      <c r="AC2" s="41"/>
+      <c r="AD2" s="41"/>
+      <c r="AE2" s="41"/>
+      <c r="AF2" s="41"/>
+      <c r="AG2" s="41"/>
+      <c r="AH2" s="41"/>
+      <c r="AI2" s="41"/>
+      <c r="AJ2" s="41"/>
+      <c r="AK2" s="41"/>
+      <c r="AL2" s="41"/>
+      <c r="AM2" s="41"/>
+      <c r="AN2" s="41"/>
+      <c r="AO2" s="41"/>
+      <c r="AP2" s="41"/>
+      <c r="AQ2" s="41"/>
+      <c r="AR2" s="41"/>
+      <c r="AS2" s="41"/>
+      <c r="AT2" s="41"/>
+      <c r="AU2" s="41"/>
+    </row>
+    <row r="3" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="A3" s="50" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="44" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="46" t="s">
+        <v>52</v>
+      </c>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="47" t="s">
+        <v>53</v>
+      </c>
+      <c r="N3" s="41"/>
+      <c r="O3" s="41"/>
+      <c r="P3" s="41"/>
+      <c r="Q3" s="41"/>
+      <c r="R3" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="S3" s="41"/>
+      <c r="T3" s="41"/>
+      <c r="U3" s="41"/>
+      <c r="V3" s="41"/>
+      <c r="W3" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="X3" s="41"/>
+      <c r="Y3" s="41"/>
+      <c r="Z3" s="45" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA3" s="41"/>
+      <c r="AB3" s="41"/>
+      <c r="AC3" s="48" t="s">
+        <v>57</v>
+      </c>
+      <c r="AD3" s="41"/>
+      <c r="AE3" s="41"/>
+      <c r="AF3" s="42" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG3" s="41"/>
+      <c r="AH3" s="41"/>
+      <c r="AI3" s="41"/>
+      <c r="AJ3" s="41"/>
+      <c r="AK3" s="41"/>
+      <c r="AL3" s="41"/>
+      <c r="AM3" s="41"/>
+      <c r="AN3" s="50" t="s">
+        <v>59</v>
+      </c>
+      <c r="AO3" s="41"/>
+      <c r="AP3" s="41"/>
+      <c r="AQ3" s="44" t="s">
+        <v>60</v>
+      </c>
+      <c r="AR3" s="41"/>
+      <c r="AS3" s="41"/>
+      <c r="AT3" s="41"/>
+      <c r="AU3" s="41"/>
+    </row>
+    <row r="4" spans="1:47" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="K4" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L4" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="M4" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="N4" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="O4" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="P4" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q4" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="R4" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="S4" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="T4" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="U4" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="V4" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="W4" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="X4" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y4" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z4" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA4" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="AB4" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="AC4" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="AD4" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="AE4" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="AF4" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="AG4" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="AH4" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="AI4" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="AJ4" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="AK4" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="AL4" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="AM4" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="AN4" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO4" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="AP4" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="AQ4" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="AR4" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AS4" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="AT4" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="AU4" s="12" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:47" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="G5" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="H5" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="I5" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="J5" s="24" t="s">
+        <v>266</v>
+      </c>
+      <c r="K5" s="21" t="s">
+        <v>271</v>
+      </c>
+      <c r="L5" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="M5" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="N5" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="O5" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="P5" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q5" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="R5" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="S5" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="T5" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="U5" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="V5" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="W5" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="X5" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y5" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z5" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="AA5" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="AB5" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="AC5" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="AD5" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="AE5" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="AF5" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="AG5" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="AH5" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI5" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="AJ5" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="AK5" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="AL5" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="AM5" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN5" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="AO5" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="AP5" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="AQ5" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="AR5" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="AS5" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="AT5" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="AU5" s="21" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="6" spans="1:47" s="30" customFormat="1" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="B6" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="C6" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="D6" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="F6" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="G6" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" s="32" t="s">
+        <v>142</v>
+      </c>
+      <c r="J6" s="33" t="s">
+        <v>267</v>
+      </c>
+      <c r="K6" s="32" t="s">
+        <v>272</v>
+      </c>
+      <c r="L6" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="M6" s="32" t="s">
+        <v>111</v>
+      </c>
+      <c r="N6" s="32" t="s">
+        <v>111</v>
+      </c>
+      <c r="O6" s="32" t="s">
+        <v>111</v>
+      </c>
+      <c r="P6" s="32" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q6" s="32" t="s">
+        <v>111</v>
+      </c>
+      <c r="R6" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="S6" s="32" t="s">
+        <v>144</v>
+      </c>
+      <c r="T6" s="32" t="s">
+        <v>144</v>
+      </c>
+      <c r="U6" s="32" t="s">
+        <v>145</v>
+      </c>
+      <c r="V6" s="32" t="s">
+        <v>146</v>
+      </c>
+      <c r="W6" s="32" t="s">
+        <v>147</v>
+      </c>
+      <c r="X6" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="Y6" s="32" t="s">
+        <v>149</v>
+      </c>
+      <c r="Z6" s="32" t="s">
+        <v>147</v>
+      </c>
+      <c r="AA6" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="AB6" s="32" t="s">
+        <v>150</v>
+      </c>
+      <c r="AC6" s="32" t="s">
+        <v>151</v>
+      </c>
+      <c r="AD6" s="32" t="s">
+        <v>152</v>
+      </c>
+      <c r="AE6" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="AF6" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG6" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="AH6" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="AI6" s="32" t="s">
+        <v>155</v>
+      </c>
+      <c r="AJ6" s="32" t="s">
+        <v>156</v>
+      </c>
+      <c r="AK6" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="AL6" s="32" t="s">
+        <v>157</v>
+      </c>
+      <c r="AM6" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="AN6" s="32" t="s">
+        <v>158</v>
+      </c>
+      <c r="AO6" s="32" t="s">
+        <v>131</v>
+      </c>
+      <c r="AP6" s="32" t="s">
+        <v>159</v>
+      </c>
+      <c r="AQ6" s="32" t="s">
+        <v>160</v>
+      </c>
+      <c r="AR6" s="32" t="s">
+        <v>134</v>
+      </c>
+      <c r="AS6" s="32" t="s">
+        <v>135</v>
+      </c>
+      <c r="AT6" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="AU6" s="32" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="7" spans="1:47" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>162</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="D7" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="34" t="s">
+        <v>163</v>
+      </c>
+      <c r="G7" s="35" t="s">
+        <v>164</v>
+      </c>
+      <c r="H7" s="35" t="s">
+        <v>165</v>
+      </c>
+      <c r="I7" s="35" t="s">
+        <v>166</v>
+      </c>
+      <c r="J7" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="K7" s="35" t="s">
+        <v>273</v>
+      </c>
+      <c r="L7" s="36" t="s">
+        <v>167</v>
+      </c>
+      <c r="M7" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="N7" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="O7" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="P7" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q7" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="R7" s="35" t="s">
+        <v>169</v>
+      </c>
+      <c r="S7" s="35" t="s">
+        <v>170</v>
+      </c>
+      <c r="T7" s="35" t="s">
+        <v>170</v>
+      </c>
+      <c r="U7" s="35" t="s">
+        <v>171</v>
+      </c>
+      <c r="V7" s="35" t="s">
+        <v>172</v>
+      </c>
+      <c r="W7" s="35" t="s">
+        <v>173</v>
+      </c>
+      <c r="X7" s="35" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y7" s="35" t="s">
+        <v>175</v>
+      </c>
+      <c r="Z7" s="35" t="s">
+        <v>173</v>
+      </c>
+      <c r="AA7" s="35" t="s">
+        <v>174</v>
+      </c>
+      <c r="AB7" s="35" t="s">
+        <v>176</v>
+      </c>
+      <c r="AC7" s="35" t="s">
+        <v>177</v>
+      </c>
+      <c r="AD7" s="35" t="s">
+        <v>178</v>
+      </c>
+      <c r="AE7" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="AF7" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="AG7" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="AH7" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI7" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="AJ7" s="35"/>
+      <c r="AK7" s="35"/>
+      <c r="AL7" s="35"/>
+      <c r="AM7" s="35"/>
+      <c r="AN7" s="35" t="s">
+        <v>180</v>
+      </c>
+      <c r="AO7" s="35" t="s">
+        <v>181</v>
+      </c>
+      <c r="AP7" s="35" t="s">
+        <v>182</v>
+      </c>
+      <c r="AQ7" s="35" t="s">
+        <v>183</v>
+      </c>
+      <c r="AR7" s="35" t="s">
+        <v>134</v>
+      </c>
+      <c r="AS7" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="AT7" s="35" t="s">
+        <v>136</v>
+      </c>
+      <c r="AU7" s="35" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="8" spans="1:47" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="27" t="s">
+        <v>184</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>185</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="27" t="s">
+        <v>186</v>
+      </c>
+      <c r="G8" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8" s="28" t="s">
+        <v>187</v>
+      </c>
+      <c r="J8" s="29" t="s">
+        <v>269</v>
+      </c>
+      <c r="K8" s="28" t="s">
+        <v>274</v>
+      </c>
+      <c r="L8" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="M8" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="N8" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="O8" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="P8" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q8" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="R8" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="S8" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="T8" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="U8" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="V8" s="28" t="s">
+        <v>190</v>
+      </c>
+      <c r="W8" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="X8" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="Y8" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="Z8" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="AA8" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="AB8" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="AC8" s="28" t="s">
+        <v>194</v>
+      </c>
+      <c r="AD8" s="28" t="s">
+        <v>195</v>
+      </c>
+      <c r="AE8" s="28" t="s">
+        <v>196</v>
+      </c>
+      <c r="AF8" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG8" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="AH8" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="AI8" s="28" t="s">
+        <v>197</v>
+      </c>
+      <c r="AJ8" s="28"/>
+      <c r="AK8" s="28"/>
+      <c r="AL8" s="28"/>
+      <c r="AM8" s="28"/>
+      <c r="AN8" s="28" t="s">
+        <v>198</v>
+      </c>
+      <c r="AO8" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="AP8" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="AQ8" s="28" t="s">
+        <v>200</v>
+      </c>
+      <c r="AR8" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="AS8" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="AT8" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="AU8" s="28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="9" spans="1:47" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="37" t="s">
+        <v>201</v>
+      </c>
+      <c r="B9" s="37" t="s">
+        <v>202</v>
+      </c>
+      <c r="C9" s="37" t="s">
+        <v>104</v>
+      </c>
+      <c r="D9" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="37" t="s">
+        <v>203</v>
+      </c>
+      <c r="G9" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" s="38" t="s">
+        <v>197</v>
+      </c>
+      <c r="J9" s="39" t="s">
+        <v>270</v>
+      </c>
+      <c r="K9" s="38" t="s">
+        <v>275</v>
+      </c>
+      <c r="L9" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="M9" s="38" t="s">
+        <v>111</v>
+      </c>
+      <c r="N9" s="38" t="s">
+        <v>168</v>
+      </c>
+      <c r="O9" s="38" t="s">
+        <v>111</v>
+      </c>
+      <c r="P9" s="38" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q9" s="38" t="s">
+        <v>111</v>
+      </c>
+      <c r="R9" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="S9" s="38" t="s">
+        <v>205</v>
+      </c>
+      <c r="T9" s="38" t="s">
+        <v>205</v>
+      </c>
+      <c r="U9" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="V9" s="38" t="s">
+        <v>206</v>
+      </c>
+      <c r="W9" s="38" t="s">
+        <v>207</v>
+      </c>
+      <c r="X9" s="38" t="s">
+        <v>208</v>
+      </c>
+      <c r="Y9" s="38" t="s">
+        <v>209</v>
+      </c>
+      <c r="Z9" s="38" t="s">
+        <v>207</v>
+      </c>
+      <c r="AA9" s="38" t="s">
+        <v>208</v>
+      </c>
+      <c r="AB9" s="38" t="s">
+        <v>210</v>
+      </c>
+      <c r="AC9" s="38" t="s">
+        <v>211</v>
+      </c>
+      <c r="AD9" s="38" t="s">
+        <v>212</v>
+      </c>
+      <c r="AE9" s="38" t="s">
+        <v>213</v>
+      </c>
+      <c r="AF9" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG9" s="38" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH9" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI9" s="38" t="s">
+        <v>214</v>
+      </c>
+      <c r="AJ9" s="38"/>
+      <c r="AK9" s="38"/>
+      <c r="AL9" s="38"/>
+      <c r="AM9" s="38"/>
+      <c r="AN9" s="38" t="s">
+        <v>215</v>
+      </c>
+      <c r="AO9" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="AP9" s="38" t="s">
+        <v>216</v>
+      </c>
+      <c r="AQ9" s="38" t="s">
+        <v>217</v>
+      </c>
+      <c r="AR9" s="38" t="s">
+        <v>134</v>
+      </c>
+      <c r="AS9" s="38" t="s">
+        <v>135</v>
+      </c>
+      <c r="AT9" s="38" t="s">
+        <v>136</v>
+      </c>
+      <c r="AU9" s="38" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="11" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="A11" s="40" t="s">
+        <v>218</v>
+      </c>
+      <c r="B11" s="41"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="41"/>
+      <c r="J11" s="41"/>
+      <c r="K11" s="41"/>
+      <c r="L11" s="41"/>
+      <c r="M11" s="41"/>
+      <c r="N11" s="41"/>
+      <c r="O11" s="41"/>
+      <c r="P11" s="41"/>
+      <c r="Q11" s="41"/>
+      <c r="R11" s="41"/>
+      <c r="S11" s="41"/>
+      <c r="T11" s="41"/>
+      <c r="U11" s="41"/>
+      <c r="V11" s="41"/>
+      <c r="W11" s="41"/>
+      <c r="X11" s="41"/>
+      <c r="Y11" s="41"/>
+      <c r="Z11" s="41"/>
+      <c r="AA11" s="41"/>
+      <c r="AB11" s="41"/>
+      <c r="AC11" s="41"/>
+      <c r="AD11" s="41"/>
+      <c r="AE11" s="41"/>
+      <c r="AF11" s="41"/>
+      <c r="AG11" s="41"/>
+      <c r="AH11" s="41"/>
+      <c r="AI11" s="41"/>
+      <c r="AJ11" s="41"/>
+      <c r="AK11" s="41"/>
+      <c r="AL11" s="41"/>
+      <c r="AM11" s="41"/>
+      <c r="AN11" s="41"/>
+      <c r="AO11" s="41"/>
+      <c r="AP11" s="41"/>
+      <c r="AQ11" s="41"/>
+      <c r="AR11" s="41"/>
+      <c r="AS11" s="41"/>
+      <c r="AT11" s="41"/>
+      <c r="AU11" s="41"/>
+    </row>
+    <row r="12" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="A12" s="22" t="s">
+        <v>219</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>220</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>221</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>222</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>223</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>224</v>
+      </c>
+      <c r="G12" s="22" t="s">
+        <v>225</v>
+      </c>
+      <c r="H12" s="22" t="s">
+        <v>226</v>
+      </c>
+      <c r="I12" s="22" t="s">
+        <v>227</v>
+      </c>
+      <c r="J12" s="26" t="s">
+        <v>228</v>
+      </c>
+      <c r="K12" s="22" t="s">
+        <v>229</v>
+      </c>
+      <c r="L12" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="M12" s="22" t="s">
+        <v>231</v>
+      </c>
+      <c r="N12" s="22" t="s">
+        <v>232</v>
+      </c>
+      <c r="O12" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="P12" s="22" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q12" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="R12" s="22" t="s">
+        <v>236</v>
+      </c>
+      <c r="S12" s="22" t="s">
+        <v>237</v>
+      </c>
+      <c r="T12" s="22" t="s">
+        <v>238</v>
+      </c>
+      <c r="U12" s="22" t="s">
+        <v>239</v>
+      </c>
+      <c r="V12" s="22" t="s">
+        <v>240</v>
+      </c>
+      <c r="W12" s="22" t="s">
+        <v>241</v>
+      </c>
+      <c r="X12" s="22" t="s">
+        <v>242</v>
+      </c>
+      <c r="Y12" s="22" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z12" s="22" t="s">
+        <v>244</v>
+      </c>
+      <c r="AA12" s="22" t="s">
+        <v>245</v>
+      </c>
+      <c r="AB12" s="22" t="s">
+        <v>246</v>
+      </c>
+      <c r="AC12" s="22" t="s">
+        <v>247</v>
+      </c>
+      <c r="AD12" s="22" t="s">
+        <v>248</v>
+      </c>
+      <c r="AE12" s="22" t="s">
+        <v>249</v>
+      </c>
+      <c r="AF12" s="22" t="s">
+        <v>250</v>
+      </c>
+      <c r="AG12" s="22" t="s">
+        <v>251</v>
+      </c>
+      <c r="AH12" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="AI12" s="22" t="s">
+        <v>253</v>
+      </c>
+      <c r="AJ12" s="22" t="s">
+        <v>254</v>
+      </c>
+      <c r="AK12" s="22" t="s">
+        <v>255</v>
+      </c>
+      <c r="AL12" s="22" t="s">
+        <v>256</v>
+      </c>
+      <c r="AM12" s="22" t="s">
+        <v>257</v>
+      </c>
+      <c r="AN12" s="22" t="s">
+        <v>258</v>
+      </c>
+      <c r="AO12" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="AP12" s="22" t="s">
+        <v>260</v>
+      </c>
+      <c r="AQ12" s="22" t="s">
+        <v>261</v>
+      </c>
+      <c r="AR12" s="22" t="s">
+        <v>262</v>
+      </c>
+      <c r="AS12" s="22" t="s">
+        <v>263</v>
+      </c>
+      <c r="AT12" s="22" t="s">
+        <v>264</v>
+      </c>
+      <c r="AU12" s="22" t="s">
+        <v>265</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A2:AU2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="W3:Y3"/>
+    <mergeCell ref="AN3:AP3"/>
+    <mergeCell ref="AQ3:AU3"/>
+    <mergeCell ref="A11:AU11"/>
+    <mergeCell ref="AF3:AM3"/>
+    <mergeCell ref="R3:V3"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="Z3:AB3"/>
+    <mergeCell ref="G3:L3"/>
+    <mergeCell ref="M3:Q3"/>
+    <mergeCell ref="AC3:AE3"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/test/resources/Reader/Apollo247_TestData.xlsx
+++ b/src/test/resources/Reader/Apollo247_TestData.xlsx
@@ -3,14 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shyam Sundar\OneDrive\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1742AD06-6983-47BA-93C3-C31A762C4029}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{C2314B8E-F19B-46CE-AD1F-0D6C2D0F43D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BMI" sheetId="1" r:id="rId1"/>
@@ -19,7 +14,8 @@
     <sheet name="FamilyMembers" sheetId="3" r:id="rId4"/>
     <sheet name="Policy_purchase_Data" sheetId="4" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="0"/>
+  <oleSize ref="A1:L19"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1204,38 +1200,38 @@
     <xf numFmtId="49" fontId="7" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1949,7 +1945,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="49" t="s">
         <v>49</v>
       </c>
       <c r="B2" s="41"/>
@@ -2000,7 +1996,7 @@
       <c r="AU2" s="41"/>
     </row>
     <row r="3" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="50" t="s">
         <v>50</v>
       </c>
       <c r="B3" s="41"/>
@@ -2010,7 +2006,7 @@
       </c>
       <c r="E3" s="41"/>
       <c r="F3" s="41"/>
-      <c r="G3" s="49" t="s">
+      <c r="G3" s="46" t="s">
         <v>52</v>
       </c>
       <c r="H3" s="41"/>
@@ -2018,36 +2014,36 @@
       <c r="J3" s="41"/>
       <c r="K3" s="41"/>
       <c r="L3" s="41"/>
-      <c r="M3" s="50" t="s">
+      <c r="M3" s="47" t="s">
         <v>53</v>
       </c>
       <c r="N3" s="41"/>
       <c r="O3" s="41"/>
       <c r="P3" s="41"/>
       <c r="Q3" s="41"/>
-      <c r="R3" s="47" t="s">
+      <c r="R3" s="43" t="s">
         <v>54</v>
       </c>
       <c r="S3" s="41"/>
       <c r="T3" s="41"/>
       <c r="U3" s="41"/>
       <c r="V3" s="41"/>
-      <c r="W3" s="43" t="s">
+      <c r="W3" s="51" t="s">
         <v>55</v>
       </c>
       <c r="X3" s="41"/>
       <c r="Y3" s="41"/>
-      <c r="Z3" s="48" t="s">
+      <c r="Z3" s="45" t="s">
         <v>56</v>
       </c>
       <c r="AA3" s="41"/>
       <c r="AB3" s="41"/>
-      <c r="AC3" s="51" t="s">
+      <c r="AC3" s="48" t="s">
         <v>57</v>
       </c>
       <c r="AD3" s="41"/>
       <c r="AE3" s="41"/>
-      <c r="AF3" s="46" t="s">
+      <c r="AF3" s="42" t="s">
         <v>58</v>
       </c>
       <c r="AG3" s="41"/>
@@ -2057,7 +2053,7 @@
       <c r="AK3" s="41"/>
       <c r="AL3" s="41"/>
       <c r="AM3" s="41"/>
-      <c r="AN3" s="42" t="s">
+      <c r="AN3" s="50" t="s">
         <v>59</v>
       </c>
       <c r="AO3" s="41"/>
@@ -2905,7 +2901,7 @@
       </c>
     </row>
     <row r="11" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A11" s="45" t="s">
+      <c r="A11" s="40" t="s">
         <v>218</v>
       </c>
       <c r="B11" s="41"/>
@@ -3100,6 +3096,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A2:AU2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="W3:Y3"/>
+    <mergeCell ref="AN3:AP3"/>
+    <mergeCell ref="AQ3:AU3"/>
     <mergeCell ref="A11:AU11"/>
     <mergeCell ref="AF3:AM3"/>
     <mergeCell ref="R3:V3"/>
@@ -3108,11 +3109,6 @@
     <mergeCell ref="G3:L3"/>
     <mergeCell ref="M3:Q3"/>
     <mergeCell ref="AC3:AE3"/>
-    <mergeCell ref="A2:AU2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="W3:Y3"/>
-    <mergeCell ref="AN3:AP3"/>
-    <mergeCell ref="AQ3:AU3"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
